--- a/InputData/indst/SoICETAF/Share of Indst Cap Expenditures That Are Financed.xlsx
+++ b/InputData/indst/SoICETAF/Share of Indst Cap Expenditures That Are Financed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\SoICETAF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F57A19-47D2-443A-B6DD-A3D65075AF37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2E009A-2237-4067-84F8-589D1EDA0408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10060" yWindow="950" windowWidth="14400" windowHeight="8210" tabRatio="644" xr2:uid="{C8F9D547-902B-4E49-8BA2-E23B0A2DC1A9}"/>
+    <workbookView xWindow="7155" yWindow="855" windowWidth="18390" windowHeight="11010" tabRatio="644" xr2:uid="{C8F9D547-902B-4E49-8BA2-E23B0A2DC1A9}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Source:</t>
   </si>
@@ -44,9 +44,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>industry-wide</t>
-  </si>
-  <si>
     <t>SoICETAF Share of Industry Capital Expenditures That Are Financed</t>
   </si>
   <si>
@@ -63,6 +60,81 @@
   </si>
   <si>
     <t>share</t>
+  </si>
+  <si>
+    <t>agriculture and forestry 01T03</t>
+  </si>
+  <si>
+    <t>coal mining 05</t>
+  </si>
+  <si>
+    <t>oil and gas extraction 06</t>
+  </si>
+  <si>
+    <t>other mining and quarrying 07T08</t>
+  </si>
+  <si>
+    <t>food beverage and tobacco 10T12</t>
+  </si>
+  <si>
+    <t>textiles apparel and leather 13T15</t>
+  </si>
+  <si>
+    <t>wood products 16</t>
+  </si>
+  <si>
+    <t>pulp paper and printing 17T18</t>
+  </si>
+  <si>
+    <t>refined petroleum and coke 19</t>
+  </si>
+  <si>
+    <t>chemicals 20</t>
+  </si>
+  <si>
+    <t>rubber and plastic products 22</t>
+  </si>
+  <si>
+    <t>glass and glass products 231</t>
+  </si>
+  <si>
+    <t>construction 41T43</t>
+  </si>
+  <si>
+    <t>cement and other nonmetallic minerals 239</t>
+  </si>
+  <si>
+    <t>iron and steel 241</t>
+  </si>
+  <si>
+    <t>other metals 242</t>
+  </si>
+  <si>
+    <t>metal products except machinery and vehicles 25</t>
+  </si>
+  <si>
+    <t>computers and electronics 26</t>
+  </si>
+  <si>
+    <t>appliances and electrical equipment 27</t>
+  </si>
+  <si>
+    <t>other machinery 28</t>
+  </si>
+  <si>
+    <t>road vehicles 29</t>
+  </si>
+  <si>
+    <t>nonroad vehicles 30</t>
+  </si>
+  <si>
+    <t>other manufacturing 31T33</t>
+  </si>
+  <si>
+    <t>energy pipelines and gas processing 352T353</t>
+  </si>
+  <si>
+    <t>water and waste 36T39</t>
   </si>
 </sst>
 </file>
@@ -482,46 +554,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F0629E-7DF7-4E6A-B1DA-78D3050B5FAD}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="87.1796875" customWidth="1"/>
+    <col min="2" max="2" width="87.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="2"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -534,27 +606,219 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.1796875" customWidth="1"/>
+    <col min="1" max="1" width="38.140625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
       <c r="B2" s="7">
-        <v>0.5</v>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/indst/SoICETAF/Share of Indst Cap Expenditures That Are Financed.xlsx
+++ b/InputData/indst/SoICETAF/Share of Indst Cap Expenditures That Are Financed.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\SoICETAF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2E009A-2237-4067-84F8-589D1EDA0408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17BF00A-5A75-469E-BC20-F6470A6C7826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7155" yWindow="855" windowWidth="18390" windowHeight="11010" tabRatio="644" xr2:uid="{C8F9D547-902B-4E49-8BA2-E23B0A2DC1A9}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="644" xr2:uid="{C8F9D547-902B-4E49-8BA2-E23B0A2DC1A9}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Source:</t>
   </si>
@@ -47,9 +47,6 @@
     <t>SoICETAF Share of Industry Capital Expenditures That Are Financed</t>
   </si>
   <si>
-    <t>none</t>
-  </si>
-  <si>
     <t>This file defines the share of industry spending on equipment</t>
   </si>
   <si>
@@ -135,6 +132,33 @@
   </si>
   <si>
     <t>water and waste 36T39</t>
+  </si>
+  <si>
+    <t>https://www.aceee.org/sites/default/files/pdfs/u2603.pdf</t>
+  </si>
+  <si>
+    <t>Efficiency Saves: Cutting Energy Waste Can Save $31,000 per Household</t>
+  </si>
+  <si>
+    <t>ACEEE</t>
+  </si>
+  <si>
+    <t>Table A8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We match the assumption made by ACEEE that 50% of industry expenditures </t>
+  </si>
+  <si>
+    <t>Equipment Leasing &amp; Finance Foundation, 2024 Horizon Report (Keybridge)</t>
+  </si>
+  <si>
+    <t>https://www.leasefoundation.org/industry-research/horizon-report/</t>
+  </si>
+  <si>
+    <t>are financed. For the agriculture &amp; construction sectors, where spending is dominated by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mobile equipment, we assume 80% is financed. </t>
   </si>
 </sst>
 </file>
@@ -142,9 +166,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,14 +180,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -215,33 +231,30 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="5">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Hyperlink 2" xfId="3" xr:uid="{84D97916-2CFC-44D4-BBA9-5F32B30F7C9D}"/>
+  <cellStyles count="4">
+    <cellStyle name="Hyperlink 2" xfId="2" xr:uid="{84D97916-2CFC-44D4-BBA9-5F32B30F7C9D}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{BDD11194-84F5-4472-8BF1-1CB91A74FE82}"/>
-    <cellStyle name="Percent 2" xfId="4" xr:uid="{6CFD2FC3-B786-4691-878C-3844B5B19D43}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{BDD11194-84F5-4472-8BF1-1CB91A74FE82}"/>
+    <cellStyle name="Percent 2" xfId="3" xr:uid="{6CFD2FC3-B786-4691-878C-3844B5B19D43}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -254,6 +267,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -551,49 +568,105 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="6">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{2D001896-A429-4EE6-A1A8-E56E09A42CD0}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;4a8fcf12-ffce-4bf0-bc9e-8724fd4f05d2&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F0629E-7DF7-4E6A-B1DA-78D3050B5FAD}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="87.140625" customWidth="1"/>
+    <col min="2" max="2" width="87.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="3"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="2"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B5" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B7" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>5</v>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -607,217 +680,217 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="38.140625" customWidth="1"/>
+    <col min="1" max="1" width="38.1796875" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" s="6">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="7">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B3">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B6">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="B7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B8" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>14</v>
       </c>
-      <c r="B8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B9" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>15</v>
       </c>
-      <c r="B9">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B10" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>16</v>
       </c>
-      <c r="B10">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B11" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>17</v>
       </c>
-      <c r="B11">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B12" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>18</v>
       </c>
-      <c r="B12">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B13" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>19</v>
       </c>
-      <c r="B13">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26">
+      <c r="B26" s="6">
         <v>0.8</v>
       </c>
     </row>
